--- a/data/trans_dic/P33B_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R1-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 11,24</t>
+          <t>1,73; 9,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,53</t>
+          <t>5,47; 14,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,84</t>
+          <t>4,4; 10,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,66</t>
+          <t>3,26; 8,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,06</t>
+          <t>6,2; 11,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,35</t>
+          <t>5,62; 9,23</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,01</t>
+          <t>6,84; 12,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,24</t>
+          <t>9,81; 14,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,8</t>
+          <t>8,92; 12,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,97</t>
+          <t>10,47; 15,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,52; 21,41</t>
+          <t>17,59; 22,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,73</t>
+          <t>14,8; 18,42</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 19,47</t>
+          <t>13,54; 19,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,41; 33,22</t>
+          <t>27,92; 33,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,3; 25,49</t>
+          <t>21,59; 25,57</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,22; 21,65</t>
+          <t>15,77; 22,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 29,62</t>
+          <t>25,96; 32,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,45; 24,37</t>
+          <t>21,74; 26,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,23; 30,32</t>
+          <t>22,8; 31,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,74; 41,2</t>
+          <t>35,49; 42,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,81; 36,0</t>
+          <t>31,26; 36,65</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,55</t>
+          <t>11,63; 13,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,35; 21,09</t>
+          <t>20,16; 22,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,7; 17,06</t>
+          <t>16,29; 18,02</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>52668</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7027; 44953</t>
+          <t>7064; 36939</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13430; 42368</t>
+          <t>19828; 53722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27652; 70210</t>
+          <t>33910; 77303</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41202</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66476</t>
+          <t>70138</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14817; 40895</t>
+          <t>15561; 41438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24925; 56571</t>
+          <t>31058; 58247</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48557; 87406</t>
+          <t>54979; 90284</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>57433</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>73812</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117058</t>
+          <t>131245</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39707; 69756</t>
+          <t>42456; 75971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52074; 77255</t>
+          <t>61009; 89236</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97703; 138044</t>
+          <t>110935; 154021</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>83899</t>
+          <t>91496</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>133920</t>
+          <t>147829</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217819</t>
+          <t>239324</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38004; 124030</t>
+          <t>73349; 110343</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>110556; 152530</t>
+          <t>129564; 165313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>137316; 267798</t>
+          <t>212753; 264650</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164391</t>
+          <t>187302</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257122</t>
+          <t>285159</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77123; 109081</t>
+          <t>82365; 117518</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>149390; 181043</t>
+          <t>169623; 205128</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>235394; 281679</t>
+          <t>262530; 310845</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>67263</t>
+          <t>75001</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>115336</t>
+          <t>127611</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182599</t>
+          <t>202611</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>56047; 79724</t>
+          <t>64199; 89734</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45471; 180037</t>
+          <t>113839; 140839</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>92251; 237832</t>
+          <t>183810; 221866</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>82386</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>162175</t>
+          <t>179808</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236431</t>
+          <t>262194</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62868; 85739</t>
+          <t>70734; 96724</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>147943; 175463</t>
+          <t>164885; 195294</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>218299; 255080</t>
+          <t>242217; 283980</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>416243</t>
+          <t>449347</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>706060</t>
+          <t>793993</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1122303</t>
+          <t>1243340</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>331078; 468750</t>
+          <t>410856; 488805</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>561591; 771546</t>
+          <t>752721; 835932</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>975390; 1214311</t>
+          <t>1183311; 1308982</t>
         </is>
       </c>
     </row>
